--- a/sampleprojects/CorporateTax/excel/states/SC_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/SC_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>DT: Determine SC Filing Requirement</t>
   </si>
@@ -148,7 +148,7 @@
     <t>Calculate SC tax at 5% flat rate; SC income tax at 5% plus license fee</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = apportionment.state_tax + apportionment.license_fee_minimum; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "SC tax calculated at 5% flat rate plus license fee ($15 minimum). Reference: SC Code 12-6-530, 12-20-50" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = apportionment.state_taxable_income * sc_apportionment.state_tax_rate; set apportionment.state_tax = the maximum of (apportionment.state_tax - apportionment.state_credits) and (0.0); set apportionment.state_tax = apportionment.state_tax + sc_apportionment.license_fee_minimum; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "SC tax calculated at 5% flat rate plus license fee ($15 minimum). Reference: SC Code 12-6-530, 12-20-50" to job.audit_trail;</t>
   </si>
   <si>
     <t>No SC nexus - no tax liability; No SC nexus - no tax</t>
@@ -160,7 +160,7 @@
     <t>Nexus but no taxable income - license fee only; No SC taxable income but license fee applies</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = apportionment.license_fee_minimum; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "No SC taxable income - license fee only ($15 minimum). NOL carryforward 15 years. Reference: SC Code 12-6-1500, 12-20-50" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = sc_apportionment.license_fee_minimum; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "No SC taxable income - license fee only ($15 minimum). NOL carryforward 15 years. Reference: SC Code 12-6-1500, 12-20-50" to job.audit_trail;</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(10 attributes)</t>
+    <t>sc_apportionment</t>
+  </si>
+  <si>
+    <t>(5 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -244,46 +244,7 @@
     <t>15.0</t>
   </si>
   <si>
-    <t>SC minimum annual license fee: $15</t>
-  </si>
-  <si>
-    <t>license_fee_rate</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>SC annual license fee rate: 0.1% (0.001) of capital and paid-in surplus</t>
-  </si>
-  <si>
-    <t>state_additions</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>SC additions: federal interest income, certain expenses, IRC 199A addback, state income tax refunds, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>South Carolina state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>SC tax credits: job development, corporate headquarters, port volume increase, research and development, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>SC subtractions: SC municipal bond interest, state income taxes, state NOL, dividend income deductions, etc.</t>
+    <t>SC annual license fee minimum: $15, added to the income tax. Reference: SC Code 12-20-50. Was read off the shared apportionment entity, where every state saw one value (#1094).</t>
   </si>
   <si>
     <t>state_tax_rate</t>
@@ -2614,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>14</v>
@@ -2629,7 +2590,7 @@
         <v>67</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>14</v>
@@ -2644,211 +2605,6 @@
         <v>14</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="8" t="s">
         <v>14</v>
       </c>
     </row>
